--- a/artfynd/A 39941-2024 artfynd.xlsx
+++ b/artfynd/A 39941-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -816,10 +816,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120349113</v>
+        <v>120349153</v>
       </c>
       <c r="B3" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,21 +832,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -903,7 +903,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Flertalet bålar av skrovellav på en gammal skadad sälg där det även växer lunglav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Flertalet bålar av lunglav på en gammal skadad sälg där det även växer skrovellav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1107,10 +1107,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120349153</v>
+        <v>120349113</v>
       </c>
       <c r="B5" t="n">
-        <v>79623</v>
+        <v>79624</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1123,21 +1123,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flertalet bålar av lunglav på en gammal skadad sälg där det även växer skrovellav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Flertalet bålar av skrovellav på en gammal skadad sälg där det även växer lunglav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1254,6 +1254,898 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120371294</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79658</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Björnmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>505350</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7012628</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Bårdlav på en sälg där det även växer lunglav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk, frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>En sälg med 38 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Medelgrov bark. # Salix caprea # En sälg med 38 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120370399</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Björnmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>505357</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7012618</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Riklig påväxt av lunglav på en lutande sälg. Vissa av bålarna är fertila med apothecier. God föryngring med många färska yngre bålar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk, frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>En lutande sälg med 31 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En lutande sälg med 31 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120370644</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Björnmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>505357</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7012618</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk, frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>En lutand</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Dead branch  # Picea abies # En lutand</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120371167</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Björnmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>505350</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7012628</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Enstaka bålar av lunglav på en sälg där det även växer bårdlav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk, frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>En sälg med 38 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Medelgrov bark. # Salix caprea # En sälg med 38 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120371664</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Björnmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>505323</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7012622</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gott om långväxt garnlav på flertalet granar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk, frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>Flertalet granar.</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies # Flertalet granar.</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120369014</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Björnmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>505356</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7012590</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Riklig påväxt av lunglav längs stor del av stammarna på en grov gammal sälg. Vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av tall, björk och sälg på frisk och frisk-fuktig mark. Mestadels träd med klenare dimensioner.</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>En gammal levande sälg med 60 cm i brösthöjdsdiameter. Består delvis av död ved med spår av hackspettar och är angripen av vedsvamp. Delar sig i två huvudstammar över brösthöjd.</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov och fårad bark. # Salix caprea # En gammal levande sälg med 60 cm i brösthöjdsdiameter. Består delvis av död ved med spår av hackspettar och är angripen av vedsvamp. Delar sig i två huvudstammar över brösthöjd.</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39941-2024 artfynd.xlsx
+++ b/artfynd/A 39941-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2147,6 +2147,1325 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120385814</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Björnmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>505172</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7012900</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Riklig påväxt av lunglav på en lutande gammal sälg. God föryngring med många färska yngre bålar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-, frisk-fuktig- och fuktig/blöt mark. Mestadels träd med klenare dimensioner</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>En gammal, lutande och nedböjd rätt grov flerstammig sälg som delvis utgörs av död ved.</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea # En gammal, lutande och nedböjd rätt grov flerstammig sälg som delvis utgörs av död ved.</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120385430</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Björnmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>505292</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7012763</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner.</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120384713</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Björnmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>505272</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7012674</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rätt gott om lunglav på en sälg där det även växer luddlav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>En tvåstammig mindre grov sälg.</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea # En tvåstammig mindre grov sälg.</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120385195</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79659</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Björnmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>505272</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7012674</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Luddlav på en sälg där det även växer lunglav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>En tvåstammig mindre grov sälg.</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea # En tvåstammig mindre grov sälg.</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120386770</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Björnmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>505101</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7012941</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Enstaka bålar av garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Barrdominerad skog med gran, tall, björk och gråal på frisk-fuktig och frisk mark. Mestadels träd med klenare dimensioner.</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120384169</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Björnmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>505249</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7012657</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Lunglav på en lutande död sälg. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner.</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>En något smalare stående lutande död sälg.</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Bark på dött träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Bark of dead wood # Salix caprea # En något smalare stående lutande död sälg.</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120385563</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Björnmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>505189</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7012870</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Enstaka garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120386369</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Björnmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>505150</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7012938</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Enstaka bålar av garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Barrdominerad skog med gran, tall, björk och gråal på frisk-fuktig och frisk mark. Mestadels träd med klenare dimensioner</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120383377</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Björnmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>505309</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7012591</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Riklig och bitvis tät påväxt av lunglav på en gammal sälg. Vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner.</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>En gammal flerstammig sälg med 44 cm i brösthöjdsdiameter. Sälgen utgörs delvis av död ved med hackspettshål.</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En gammal flerstammig sälg med 44 cm i brösthöjdsdiameter. Sälgen utgörs delvis av död ved med hackspettshål.</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39941-2024 artfynd.xlsx
+++ b/artfynd/A 39941-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120348975</v>
+        <v>120349113</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505501</v>
+        <v>505456</v>
       </c>
       <c r="R2" t="n">
-        <v>7012484</v>
+        <v>7012524</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -758,7 +762,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Lite garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Flertalet bålar av skrovellav på en gammal skadad sälg där det även växer lunglav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,32 +777,37 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Våtmark med gran</t>
+          <t>Våtmark med barrträd</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Gles grandominerad skog på fuktig/blöt mark. Mestadels klena träd.</t>
+          <t>Gles barrdominerad skog på fuktig/blöt mark. Mestadels klena träd.</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>En levande men mycket skadad sälg.</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En levande men mycket skadad sälg.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -816,10 +825,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120349153</v>
+        <v>120348975</v>
       </c>
       <c r="B3" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,30 +841,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -863,10 +868,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505456</v>
+        <v>505501</v>
       </c>
       <c r="R3" t="n">
-        <v>7012524</v>
+        <v>7012484</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -903,7 +908,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Flertalet bålar av lunglav på en gammal skadad sälg där det även växer skrovellav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Lite garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,37 +923,32 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Våtmark med barrträd</t>
+          <t>Våtmark med gran</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Gles barrdominerad skog på fuktig/blöt mark. Mestadels klena träd.</t>
+          <t>Gles grandominerad skog på fuktig/blöt mark. Mestadels klena träd.</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>En levande men mycket skadad sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En levande men mycket skadad sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120349113</v>
+        <v>120349153</v>
       </c>
       <c r="B5" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1123,21 +1123,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flertalet bålar av skrovellav på en gammal skadad sälg där det även växer lunglav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Flertalet bålar av lunglav på en gammal skadad sälg där det även växer skrovellav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1407,7 +1407,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120370399</v>
+        <v>120371167</v>
       </c>
       <c r="B7" t="n">
         <v>79623</v>
@@ -1444,7 +1444,7 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505357</v>
+        <v>505350</v>
       </c>
       <c r="R7" t="n">
-        <v>7012618</v>
+        <v>7012628</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Riklig påväxt av lunglav på en lutande sälg. Vissa av bålarna är fertila med apothecier. God föryngring med många färska yngre bålar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Enstaka bålar av lunglav på en sälg där det även växer bårdlav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>En lutande sälg med 31 cm i brösthöjdsdiameter.</t>
+          <t>En sälg med 38 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En lutande sälg med 31 cm i brösthöjdsdiameter.</t>
+          <t>Bark on living woody plant # Medelgrov bark. # Salix caprea # En sälg med 38 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1557,7 +1557,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120370644</v>
+        <v>120371664</v>
       </c>
       <c r="B8" t="n">
         <v>78542</v>
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505357</v>
+        <v>505323</v>
       </c>
       <c r="R8" t="n">
-        <v>7012618</v>
+        <v>7012622</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Gott om långväxt garnlav på flertalet granar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1675,17 +1675,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>En lutand</t>
+          <t>Flertalet granar.</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies # En lutand</t>
+          <t>Branch on living tree # Picea abies # Flertalet granar.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1703,7 +1703,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120371167</v>
+        <v>120370399</v>
       </c>
       <c r="B9" t="n">
         <v>79623</v>
@@ -1740,7 +1740,7 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505350</v>
+        <v>505357</v>
       </c>
       <c r="R9" t="n">
-        <v>7012628</v>
+        <v>7012618</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav på en sälg där det även växer bårdlav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Riklig påväxt av lunglav på en lutande sälg. Vissa av bålarna är fertila med apothecier. God föryngring med många färska yngre bålar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>En sälg med 38 cm i brösthöjdsdiameter.</t>
+          <t>En lutande sälg med 31 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Medelgrov bark. # Salix caprea # En sälg med 38 cm i brösthöjdsdiameter.</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En lutande sälg med 31 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1853,7 +1853,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120371664</v>
+        <v>120370644</v>
       </c>
       <c r="B10" t="n">
         <v>78542</v>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505323</v>
+        <v>505357</v>
       </c>
       <c r="R10" t="n">
-        <v>7012622</v>
+        <v>7012618</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flertalet granar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1971,17 +1971,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>Flertalet granar.</t>
+          <t>En lutand</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flertalet granar.</t>
+          <t>Dead branch  # Picea abies # En lutand</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2149,7 +2149,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120385814</v>
+        <v>120384713</v>
       </c>
       <c r="B12" t="n">
         <v>79623</v>
@@ -2196,13 +2196,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505172</v>
+        <v>505272</v>
       </c>
       <c r="R12" t="n">
-        <v>7012900</v>
+        <v>7012674</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Riklig påväxt av lunglav på en lutande gammal sälg. God föryngring med många färska yngre bålar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Rätt gott om lunglav på en sälg där det även växer luddlav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-, frisk-fuktig- och fuktig/blöt mark. Mestadels träd med klenare dimensioner</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>En gammal, lutande och nedböjd rätt grov flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>En tvåstammig mindre grov sälg.</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En gammal, lutande och nedböjd rätt grov flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Bark on living woody plant # Salix caprea # En tvåstammig mindre grov sälg.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2299,10 +2299,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120385430</v>
+        <v>120383377</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2315,26 +2315,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2342,10 +2346,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505292</v>
+        <v>505309</v>
       </c>
       <c r="R13" t="n">
-        <v>7012763</v>
+        <v>7012591</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2382,7 +2386,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Måttligt med garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Riklig och bitvis tät påväxt av lunglav på en gammal sälg. Vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2407,27 +2411,27 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>Flera granar.</t>
+          <t>En gammal flerstammig sälg med 44 cm i brösthöjdsdiameter. Sälgen utgörs delvis av död ved med hackspettshål.</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En gammal flerstammig sälg med 44 cm i brösthöjdsdiameter. Sälgen utgörs delvis av död ved med hackspettshål.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2445,10 +2449,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120384713</v>
+        <v>120385430</v>
       </c>
       <c r="B14" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2461,30 +2465,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2492,13 +2492,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505272</v>
+        <v>505292</v>
       </c>
       <c r="R14" t="n">
-        <v>7012674</v>
+        <v>7012763</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rätt gott om lunglav på en sälg där det även växer luddlav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Måttligt med garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2552,32 +2552,32 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>En tvåstammig mindre grov sälg.</t>
+          <t>Flera granar.</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En tvåstammig mindre grov sälg.</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2595,10 +2595,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120385195</v>
+        <v>120385814</v>
       </c>
       <c r="B15" t="n">
-        <v>79659</v>
+        <v>79623</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2607,32 +2607,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2642,13 +2642,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505272</v>
+        <v>505172</v>
       </c>
       <c r="R15" t="n">
-        <v>7012674</v>
+        <v>7012900</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Luddlav på en sälg där det även växer lunglav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Riklig påväxt av lunglav på en lutande gammal sälg. God föryngring med många färska yngre bålar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-, frisk-fuktig- och fuktig/blöt mark. Mestadels träd med klenare dimensioner</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>En tvåstammig mindre grov sälg.</t>
+          <t>En gammal, lutande och nedböjd rätt grov flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En tvåstammig mindre grov sälg.</t>
+          <t>Bark on living woody plant # Salix caprea # En gammal, lutande och nedböjd rätt grov flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2745,7 +2745,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120386770</v>
+        <v>120385563</v>
       </c>
       <c r="B16" t="n">
         <v>78542</v>
@@ -2788,10 +2788,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505101</v>
+        <v>505189</v>
       </c>
       <c r="R16" t="n">
-        <v>7012941</v>
+        <v>7012870</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Enstaka bålar av garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Enstaka garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och gråal på frisk-fuktig och frisk mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2886,10 +2886,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120384169</v>
+        <v>120385195</v>
       </c>
       <c r="B17" t="n">
-        <v>79623</v>
+        <v>79659</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2898,32 +2898,32 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2933,13 +2933,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505249</v>
+        <v>505272</v>
       </c>
       <c r="R17" t="n">
-        <v>7012657</v>
+        <v>7012674</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Lunglav på en lutande död sälg. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Luddlav på en sälg där det även växer lunglav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -3008,17 +3008,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>En något smalare stående lutande död sälg.</t>
+          <t>En tvåstammig mindre grov sälg.</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En något smalare stående lutande död sälg.</t>
+          <t>Bark on living woody plant # Salix caprea # En tvåstammig mindre grov sälg.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -3036,7 +3036,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120385563</v>
+        <v>120386770</v>
       </c>
       <c r="B18" t="n">
         <v>78542</v>
@@ -3079,10 +3079,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505189</v>
+        <v>505101</v>
       </c>
       <c r="R18" t="n">
-        <v>7012870</v>
+        <v>7012941</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Enstaka garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Enstaka bålar av garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner</t>
+          <t>Barrdominerad skog med gran, tall, björk och gråal på frisk-fuktig och frisk mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -3318,7 +3318,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120383377</v>
+        <v>120384169</v>
       </c>
       <c r="B20" t="n">
         <v>79623</v>
@@ -3355,7 +3355,7 @@
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>505309</v>
+        <v>505249</v>
       </c>
       <c r="R20" t="n">
-        <v>7012591</v>
+        <v>7012657</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Riklig och bitvis tät påväxt av lunglav på en gammal sälg. Vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Lunglav på en lutande död sälg. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>En gammal flerstammig sälg med 44 cm i brösthöjdsdiameter. Sälgen utgörs delvis av död ved med hackspettshål.</t>
+          <t>En något smalare stående lutande död sälg.</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En gammal flerstammig sälg med 44 cm i brösthöjdsdiameter. Sälgen utgörs delvis av död ved med hackspettshål.</t>
+          <t>Bark of dead wood # Salix caprea # En något smalare stående lutande död sälg.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 39941-2024 artfynd.xlsx
+++ b/artfynd/A 39941-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120349113</v>
+        <v>120349153</v>
       </c>
       <c r="B2" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -762,7 +762,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Flertalet bålar av skrovellav på en gammal skadad sälg där det även växer lunglav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Flertalet bålar av lunglav på en gammal skadad sälg där det även växer skrovellav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -966,10 +966,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120349281</v>
+        <v>120349113</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -982,26 +982,30 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1009,10 +1013,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505418</v>
+        <v>505456</v>
       </c>
       <c r="R4" t="n">
-        <v>7012531</v>
+        <v>7012524</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1049,7 +1053,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Flertalet bålar av skrovellav på en gammal skadad sälg där det även växer lunglav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1064,32 +1068,37 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Våtmark med barrträd</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Klenvuxen grandominerad skog på frisk-fuktig- och fuktig mark. Skogsbruksåtgärd genom röjning förekommer här.</t>
+          <t>Gles barrdominerad skog på fuktig/blöt mark. Mestadels klena träd.</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>En levande men mycket skadad sälg.</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En levande men mycket skadad sälg.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1107,10 +1116,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120349153</v>
+        <v>120349281</v>
       </c>
       <c r="B5" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1123,30 +1132,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1154,10 +1159,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505456</v>
+        <v>505418</v>
       </c>
       <c r="R5" t="n">
-        <v>7012524</v>
+        <v>7012531</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1194,7 +1199,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flertalet bålar av lunglav på en gammal skadad sälg där det även växer skrovellav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1209,37 +1214,32 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Våtmark med barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Gles barrdominerad skog på fuktig/blöt mark. Mestadels klena träd.</t>
+          <t>Klenvuxen grandominerad skog på frisk-fuktig- och fuktig mark. Skogsbruksåtgärd genom röjning förekommer här.</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>En levande men mycket skadad sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En levande men mycket skadad sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120371294</v>
+        <v>120371664</v>
       </c>
       <c r="B6" t="n">
-        <v>79658</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1269,20 +1269,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1292,11 +1292,7 @@
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1304,10 +1300,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505350</v>
+        <v>505323</v>
       </c>
       <c r="R6" t="n">
-        <v>7012628</v>
+        <v>7012622</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1344,7 +1340,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Bårdlav på en sälg där det även växer lunglav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Gott om långväxt garnlav på flertalet granar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1369,27 +1365,27 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>En sälg med 38 cm i brösthöjdsdiameter.</t>
+          <t>Flertalet granar.</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Medelgrov bark. # Salix caprea # En sälg med 38 cm i brösthöjdsdiameter.</t>
+          <t>Branch on living tree # Picea abies # Flertalet granar.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1407,10 +1403,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120371167</v>
+        <v>120371294</v>
       </c>
       <c r="B7" t="n">
-        <v>79623</v>
+        <v>79658</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1419,25 +1415,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1494,7 +1490,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav på en sälg där det även växer bårdlav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Bårdlav på en sälg där det även växer lunglav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1557,10 +1553,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120371664</v>
+        <v>120370399</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1573,26 +1569,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505323</v>
+        <v>505357</v>
       </c>
       <c r="R8" t="n">
-        <v>7012622</v>
+        <v>7012618</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flertalet granar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Riklig påväxt av lunglav på en lutande sälg. Vissa av bålarna är fertila med apothecier. God föryngring med många färska yngre bålar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1665,27 +1665,27 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>Flertalet granar.</t>
+          <t>En lutande sälg med 31 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flertalet granar.</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En lutande sälg med 31 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1703,10 +1703,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120370399</v>
+        <v>120370644</v>
       </c>
       <c r="B9" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1719,30 +1719,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1790,7 +1786,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Riklig påväxt av lunglav på en lutande sälg. Vissa av bålarna är fertila med apothecier. God föryngring med många färska yngre bålar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1815,27 +1811,27 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>En lutande sälg med 31 cm i brösthöjdsdiameter.</t>
+          <t>En lutand</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En lutande sälg med 31 cm i brösthöjdsdiameter.</t>
+          <t>Dead branch  # Picea abies # En lutand</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1853,10 +1849,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120370644</v>
+        <v>120371167</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1869,26 +1865,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505357</v>
+        <v>505350</v>
       </c>
       <c r="R10" t="n">
-        <v>7012618</v>
+        <v>7012628</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Enstaka bålar av lunglav på en sälg där det även växer bårdlav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1961,27 +1961,27 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>En lutand</t>
+          <t>En sälg med 38 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies # En lutand</t>
+          <t>Bark on living woody plant # Medelgrov bark. # Salix caprea # En sälg med 38 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2299,10 +2299,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120383377</v>
+        <v>120386770</v>
       </c>
       <c r="B13" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2315,30 +2315,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2346,10 +2342,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505309</v>
+        <v>505101</v>
       </c>
       <c r="R13" t="n">
-        <v>7012591</v>
+        <v>7012941</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2386,7 +2382,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Riklig och bitvis tät påväxt av lunglav på en gammal sälg. Vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Enstaka bålar av garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2406,32 +2402,27 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Barrdominerad skog med gran, tall, björk och gråal på frisk-fuktig och frisk mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>En gammal flerstammig sälg med 44 cm i brösthöjdsdiameter. Sälgen utgörs delvis av död ved med hackspettshål.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En gammal flerstammig sälg med 44 cm i brösthöjdsdiameter. Sälgen utgörs delvis av död ved med hackspettshål.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2449,7 +2440,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120385430</v>
+        <v>120386369</v>
       </c>
       <c r="B14" t="n">
         <v>78542</v>
@@ -2492,10 +2483,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505292</v>
+        <v>505150</v>
       </c>
       <c r="R14" t="n">
-        <v>7012763</v>
+        <v>7012938</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2532,7 +2523,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Måttligt med garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Enstaka bålar av garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2552,7 +2543,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Barrdominerad skog med gran, tall, björk och gråal på frisk-fuktig och frisk mark. Mestadels träd med klenare dimensioner</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2565,11 +2556,6 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>Flera granar.</t>
-        </is>
-      </c>
       <c r="AM14" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -2577,7 +2563,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2595,7 +2581,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120385814</v>
+        <v>120383377</v>
       </c>
       <c r="B15" t="n">
         <v>79623</v>
@@ -2632,7 +2618,7 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2642,10 +2628,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505172</v>
+        <v>505309</v>
       </c>
       <c r="R15" t="n">
-        <v>7012900</v>
+        <v>7012591</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2682,7 +2668,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Riklig påväxt av lunglav på en lutande gammal sälg. God föryngring med många färska yngre bålar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Riklig och bitvis tät påväxt av lunglav på en gammal sälg. Vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2702,7 +2688,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-, frisk-fuktig- och fuktig/blöt mark. Mestadels träd med klenare dimensioner</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2717,7 +2703,7 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>En gammal, lutande och nedböjd rätt grov flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>En gammal flerstammig sälg med 44 cm i brösthöjdsdiameter. Sälgen utgörs delvis av död ved med hackspettshål.</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -2727,7 +2713,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En gammal, lutande och nedböjd rätt grov flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En gammal flerstammig sälg med 44 cm i brösthöjdsdiameter. Sälgen utgörs delvis av död ved med hackspettshål.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2745,10 +2731,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120385563</v>
+        <v>120385195</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>79659</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2757,30 +2743,34 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2788,13 +2778,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505189</v>
+        <v>505272</v>
       </c>
       <c r="R16" t="n">
-        <v>7012870</v>
+        <v>7012674</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2828,7 +2818,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Enstaka garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Luddlav på en sälg där det även växer lunglav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2848,27 +2838,32 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>En tvåstammig mindre grov sälg.</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En tvåstammig mindre grov sälg.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2886,10 +2881,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120385195</v>
+        <v>120385814</v>
       </c>
       <c r="B17" t="n">
-        <v>79659</v>
+        <v>79623</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2898,32 +2893,32 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2933,13 +2928,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505272</v>
+        <v>505172</v>
       </c>
       <c r="R17" t="n">
-        <v>7012674</v>
+        <v>7012900</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2973,7 +2968,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Luddlav på en sälg där det även växer lunglav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Riklig påväxt av lunglav på en lutande gammal sälg. God föryngring med många färska yngre bålar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2993,7 +2988,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-, frisk-fuktig- och fuktig/blöt mark. Mestadels träd med klenare dimensioner</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -3008,7 +3003,7 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>En tvåstammig mindre grov sälg.</t>
+          <t>En gammal, lutande och nedböjd rätt grov flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -3018,7 +3013,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En tvåstammig mindre grov sälg.</t>
+          <t>Bark on living woody plant # Salix caprea # En gammal, lutande och nedböjd rätt grov flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -3036,7 +3031,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120386770</v>
+        <v>120385563</v>
       </c>
       <c r="B18" t="n">
         <v>78542</v>
@@ -3079,10 +3074,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505101</v>
+        <v>505189</v>
       </c>
       <c r="R18" t="n">
-        <v>7012941</v>
+        <v>7012870</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -3119,7 +3114,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Enstaka bålar av garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Enstaka garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3139,7 +3134,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och gråal på frisk-fuktig och frisk mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -3177,7 +3172,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120386369</v>
+        <v>120385430</v>
       </c>
       <c r="B19" t="n">
         <v>78542</v>
@@ -3220,10 +3215,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505150</v>
+        <v>505292</v>
       </c>
       <c r="R19" t="n">
-        <v>7012938</v>
+        <v>7012763</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -3260,7 +3255,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Enstaka bålar av garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Måttligt med garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3280,7 +3275,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och gråal på frisk-fuktig och frisk mark. Mestadels träd med klenare dimensioner</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3293,6 +3288,11 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
       <c r="AM19" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -3300,7 +3300,7 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>

--- a/artfynd/A 39941-2024 artfynd.xlsx
+++ b/artfynd/A 39941-2024 artfynd.xlsx
@@ -1257,10 +1257,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120371664</v>
+        <v>120371167</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1273,26 +1273,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1300,10 +1304,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505323</v>
+        <v>505350</v>
       </c>
       <c r="R6" t="n">
-        <v>7012622</v>
+        <v>7012628</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1340,7 +1344,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flertalet granar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Enstaka bålar av lunglav på en sälg där det även växer bårdlav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1365,27 +1369,27 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Flertalet granar.</t>
+          <t>En sälg med 38 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flertalet granar.</t>
+          <t>Bark on living woody plant # Medelgrov bark. # Salix caprea # En sälg med 38 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1703,7 +1707,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120370644</v>
+        <v>120371664</v>
       </c>
       <c r="B9" t="n">
         <v>78542</v>
@@ -1746,10 +1750,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505357</v>
+        <v>505323</v>
       </c>
       <c r="R9" t="n">
-        <v>7012618</v>
+        <v>7012622</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1786,7 +1790,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Gott om långväxt garnlav på flertalet granar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1821,17 +1825,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>En lutand</t>
+          <t>Flertalet granar.</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies # En lutand</t>
+          <t>Branch on living tree # Picea abies # Flertalet granar.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1849,10 +1853,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120371167</v>
+        <v>120370644</v>
       </c>
       <c r="B10" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1865,30 +1869,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505350</v>
+        <v>505357</v>
       </c>
       <c r="R10" t="n">
-        <v>7012628</v>
+        <v>7012618</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav på en sälg där det även växer bårdlav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1961,27 +1961,27 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>En sälg med 38 cm i brösthöjdsdiameter.</t>
+          <t>En lutand</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Medelgrov bark. # Salix caprea # En sälg med 38 cm i brösthöjdsdiameter.</t>
+          <t>Dead branch  # Picea abies # En lutand</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -2149,7 +2149,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120384713</v>
+        <v>120383377</v>
       </c>
       <c r="B12" t="n">
         <v>79623</v>
@@ -2186,7 +2186,7 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2196,13 +2196,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505272</v>
+        <v>505309</v>
       </c>
       <c r="R12" t="n">
-        <v>7012674</v>
+        <v>7012591</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rätt gott om lunglav på en sälg där det även växer luddlav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Riklig och bitvis tät påväxt av lunglav på en gammal sälg. Vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>En tvåstammig mindre grov sälg.</t>
+          <t>En gammal flerstammig sälg med 44 cm i brösthöjdsdiameter. Sälgen utgörs delvis av död ved med hackspettshål.</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En tvåstammig mindre grov sälg.</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En gammal flerstammig sälg med 44 cm i brösthöjdsdiameter. Sälgen utgörs delvis av död ved med hackspettshål.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2299,10 +2299,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120386770</v>
+        <v>120384713</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2315,26 +2315,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2342,13 +2346,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505101</v>
+        <v>505272</v>
       </c>
       <c r="R13" t="n">
-        <v>7012941</v>
+        <v>7012674</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2382,7 +2386,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Enstaka bålar av garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Rätt gott om lunglav på en sälg där det även växer luddlav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2402,27 +2406,32 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och gråal på frisk-fuktig och frisk mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>En tvåstammig mindre grov sälg.</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En tvåstammig mindre grov sälg.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2440,10 +2449,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120386369</v>
+        <v>120385814</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2456,26 +2465,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2483,10 +2496,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505150</v>
+        <v>505172</v>
       </c>
       <c r="R14" t="n">
-        <v>7012938</v>
+        <v>7012900</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2523,7 +2536,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Enstaka bålar av garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Riklig påväxt av lunglav på en lutande gammal sälg. God föryngring med många färska yngre bålar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2543,27 +2556,32 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och gråal på frisk-fuktig och frisk mark. Mestadels träd med klenare dimensioner</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-, frisk-fuktig- och fuktig/blöt mark. Mestadels träd med klenare dimensioner</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>En gammal, lutande och nedböjd rätt grov flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En gammal, lutande och nedböjd rätt grov flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2581,10 +2599,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120383377</v>
+        <v>120385563</v>
       </c>
       <c r="B15" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2597,30 +2615,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2628,10 +2642,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505309</v>
+        <v>505189</v>
       </c>
       <c r="R15" t="n">
-        <v>7012591</v>
+        <v>7012870</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2668,7 +2682,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Riklig och bitvis tät påväxt av lunglav på en gammal sälg. Vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Enstaka garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2688,32 +2702,27 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>En gammal flerstammig sälg med 44 cm i brösthöjdsdiameter. Sälgen utgörs delvis av död ved med hackspettshål.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En gammal flerstammig sälg med 44 cm i brösthöjdsdiameter. Sälgen utgörs delvis av död ved med hackspettshål.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2731,10 +2740,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120385195</v>
+        <v>120386770</v>
       </c>
       <c r="B16" t="n">
-        <v>79659</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2743,34 +2752,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2778,13 +2783,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505272</v>
+        <v>505101</v>
       </c>
       <c r="R16" t="n">
-        <v>7012674</v>
+        <v>7012941</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2818,7 +2823,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Luddlav på en sälg där det även växer lunglav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Enstaka bålar av garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2838,32 +2843,27 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Barrdominerad skog med gran, tall, björk och gråal på frisk-fuktig och frisk mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>En tvåstammig mindre grov sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En tvåstammig mindre grov sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2881,10 +2881,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120385814</v>
+        <v>120386369</v>
       </c>
       <c r="B17" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2897,30 +2897,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2928,10 +2924,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505172</v>
+        <v>505150</v>
       </c>
       <c r="R17" t="n">
-        <v>7012900</v>
+        <v>7012938</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2968,7 +2964,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Riklig påväxt av lunglav på en lutande gammal sälg. God föryngring med många färska yngre bålar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Enstaka bålar av garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2988,32 +2984,27 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-, frisk-fuktig- och fuktig/blöt mark. Mestadels träd med klenare dimensioner</t>
+          <t>Barrdominerad skog med gran, tall, björk och gråal på frisk-fuktig och frisk mark. Mestadels träd med klenare dimensioner</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>En gammal, lutande och nedböjd rätt grov flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En gammal, lutande och nedböjd rätt grov flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -3031,10 +3022,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120385563</v>
+        <v>120385195</v>
       </c>
       <c r="B18" t="n">
-        <v>78542</v>
+        <v>79659</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -3043,30 +3034,34 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -3074,13 +3069,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505189</v>
+        <v>505272</v>
       </c>
       <c r="R18" t="n">
-        <v>7012870</v>
+        <v>7012674</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3114,7 +3109,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Enstaka garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Luddlav på en sälg där det även växer lunglav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3134,27 +3129,32 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>En tvåstammig mindre grov sälg.</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En tvåstammig mindre grov sälg.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>

--- a/artfynd/A 39941-2024 artfynd.xlsx
+++ b/artfynd/A 39941-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120349153</v>
+        <v>120348975</v>
       </c>
       <c r="B2" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,30 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505456</v>
+        <v>505501</v>
       </c>
       <c r="R2" t="n">
-        <v>7012524</v>
+        <v>7012484</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Flertalet bålar av lunglav på en gammal skadad sälg där det även växer skrovellav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Lite garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,37 +773,32 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Våtmark med barrträd</t>
+          <t>Våtmark med gran</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Gles barrdominerad skog på fuktig/blöt mark. Mestadels klena träd.</t>
+          <t>Gles grandominerad skog på fuktig/blöt mark. Mestadels klena träd.</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>En levande men mycket skadad sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En levande men mycket skadad sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -825,10 +816,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120348975</v>
+        <v>120349113</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -841,26 +832,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -868,10 +863,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505501</v>
+        <v>505456</v>
       </c>
       <c r="R3" t="n">
-        <v>7012484</v>
+        <v>7012524</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -908,7 +903,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Lite garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Flertalet bålar av skrovellav på en gammal skadad sälg där det även växer lunglav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,32 +918,37 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Våtmark med gran</t>
+          <t>Våtmark med barrträd</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Gles grandominerad skog på fuktig/blöt mark. Mestadels klena träd.</t>
+          <t>Gles barrdominerad skog på fuktig/blöt mark. Mestadels klena träd.</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>En levande men mycket skadad sälg.</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En levande men mycket skadad sälg.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -966,10 +966,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120349113</v>
+        <v>120349153</v>
       </c>
       <c r="B4" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Flertalet bålar av skrovellav på en gammal skadad sälg där det även växer lunglav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Flertalet bålar av lunglav på en gammal skadad sälg där det även växer skrovellav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1257,10 +1257,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120371167</v>
+        <v>120371664</v>
       </c>
       <c r="B6" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1273,30 +1273,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1304,10 +1300,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505350</v>
+        <v>505323</v>
       </c>
       <c r="R6" t="n">
-        <v>7012628</v>
+        <v>7012622</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1344,7 +1340,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav på en sälg där det även växer bårdlav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Gott om långväxt garnlav på flertalet granar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1369,27 +1365,27 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>En sälg med 38 cm i brösthöjdsdiameter.</t>
+          <t>Flertalet granar.</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Medelgrov bark. # Salix caprea # En sälg med 38 cm i brösthöjdsdiameter.</t>
+          <t>Branch on living tree # Picea abies # Flertalet granar.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1407,10 +1403,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120371294</v>
+        <v>120370644</v>
       </c>
       <c r="B7" t="n">
-        <v>79658</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1419,20 +1415,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1442,11 +1438,7 @@
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1454,10 +1446,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505350</v>
+        <v>505357</v>
       </c>
       <c r="R7" t="n">
-        <v>7012628</v>
+        <v>7012618</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1494,7 +1486,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Bårdlav på en sälg där det även växer lunglav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1519,27 +1511,27 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>En sälg med 38 cm i brösthöjdsdiameter.</t>
+          <t>En lutand</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Medelgrov bark. # Salix caprea # En sälg med 38 cm i brösthöjdsdiameter.</t>
+          <t>Dead branch  # Picea abies # En lutand</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1557,7 +1549,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120370399</v>
+        <v>120371167</v>
       </c>
       <c r="B8" t="n">
         <v>79623</v>
@@ -1594,7 +1586,7 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1604,10 +1596,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505357</v>
+        <v>505350</v>
       </c>
       <c r="R8" t="n">
-        <v>7012618</v>
+        <v>7012628</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1644,7 +1636,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Riklig påväxt av lunglav på en lutande sälg. Vissa av bålarna är fertila med apothecier. God föryngring med många färska yngre bålar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Enstaka bålar av lunglav på en sälg där det även växer bårdlav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1679,7 +1671,7 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>En lutande sälg med 31 cm i brösthöjdsdiameter.</t>
+          <t>En sälg med 38 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -1689,7 +1681,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En lutande sälg med 31 cm i brösthöjdsdiameter.</t>
+          <t>Bark on living woody plant # Medelgrov bark. # Salix caprea # En sälg med 38 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1707,10 +1699,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120371664</v>
+        <v>120371294</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>79658</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1719,20 +1711,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1742,7 +1734,11 @@
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1750,10 +1746,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505323</v>
+        <v>505350</v>
       </c>
       <c r="R9" t="n">
-        <v>7012622</v>
+        <v>7012628</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1790,7 +1786,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flertalet granar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Bårdlav på en sälg där det även växer lunglav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1815,27 +1811,27 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>Flertalet granar.</t>
+          <t>En sälg med 38 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flertalet granar.</t>
+          <t>Bark on living woody plant # Medelgrov bark. # Salix caprea # En sälg med 38 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1853,10 +1849,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120370644</v>
+        <v>120369014</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1869,26 +1865,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505357</v>
+        <v>505356</v>
       </c>
       <c r="R10" t="n">
-        <v>7012618</v>
+        <v>7012590</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Riklig påväxt av lunglav längs stor del av stammarna på en grov gammal sälg. Vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1951,37 +1951,37 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk, frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Grandominerad skog med inslag av tall, björk och sälg på frisk och frisk-fuktig mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>En lutand</t>
+          <t>En gammal levande sälg med 60 cm i brösthöjdsdiameter. Består delvis av död ved med spår av hackspettar och är angripen av vedsvamp. Delar sig i två huvudstammar över brösthöjd.</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies # En lutand</t>
+          <t>Bark on living woody plant # Grov och fårad bark. # Salix caprea # En gammal levande sälg med 60 cm i brösthöjdsdiameter. Består delvis av död ved med spår av hackspettar och är angripen av vedsvamp. Delar sig i två huvudstammar över brösthöjd.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1999,7 +1999,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120369014</v>
+        <v>120370399</v>
       </c>
       <c r="B11" t="n">
         <v>79623</v>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505356</v>
+        <v>505357</v>
       </c>
       <c r="R11" t="n">
-        <v>7012590</v>
+        <v>7012618</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Riklig påväxt av lunglav längs stor del av stammarna på en grov gammal sälg. Vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Riklig påväxt av lunglav på en lutande sälg. Vissa av bålarna är fertila med apothecier. God föryngring med många färska yngre bålar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Grandominerad skog med inslag av tall, björk och sälg på frisk och frisk-fuktig mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk, frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>En gammal levande sälg med 60 cm i brösthöjdsdiameter. Består delvis av död ved med spår av hackspettar och är angripen av vedsvamp. Delar sig i två huvudstammar över brösthöjd.</t>
+          <t>En lutande sälg med 31 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov och fårad bark. # Salix caprea # En gammal levande sälg med 60 cm i brösthöjdsdiameter. Består delvis av död ved med spår av hackspettar och är angripen av vedsvamp. Delar sig i två huvudstammar över brösthöjd.</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En lutande sälg med 31 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2149,7 +2149,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120383377</v>
+        <v>120384169</v>
       </c>
       <c r="B12" t="n">
         <v>79623</v>
@@ -2186,7 +2186,7 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505309</v>
+        <v>505249</v>
       </c>
       <c r="R12" t="n">
-        <v>7012591</v>
+        <v>7012657</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Riklig och bitvis tät påväxt av lunglav på en gammal sälg. Vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Lunglav på en lutande död sälg. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2271,17 +2271,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>En gammal flerstammig sälg med 44 cm i brösthöjdsdiameter. Sälgen utgörs delvis av död ved med hackspettshål.</t>
+          <t>En något smalare stående lutande död sälg.</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En gammal flerstammig sälg med 44 cm i brösthöjdsdiameter. Sälgen utgörs delvis av död ved med hackspettshål.</t>
+          <t>Bark of dead wood # Salix caprea # En något smalare stående lutande död sälg.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120385814</v>
+        <v>120386369</v>
       </c>
       <c r="B14" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2465,30 +2465,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2496,10 +2492,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505172</v>
+        <v>505150</v>
       </c>
       <c r="R14" t="n">
-        <v>7012900</v>
+        <v>7012938</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2536,7 +2532,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Riklig påväxt av lunglav på en lutande gammal sälg. God föryngring med många färska yngre bålar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Enstaka bålar av garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2556,32 +2552,27 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-, frisk-fuktig- och fuktig/blöt mark. Mestadels träd med klenare dimensioner</t>
+          <t>Barrdominerad skog med gran, tall, björk och gråal på frisk-fuktig och frisk mark. Mestadels träd med klenare dimensioner</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>En gammal, lutande och nedböjd rätt grov flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En gammal, lutande och nedböjd rätt grov flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2599,7 +2590,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120385563</v>
+        <v>120386770</v>
       </c>
       <c r="B15" t="n">
         <v>78542</v>
@@ -2642,10 +2633,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505189</v>
+        <v>505101</v>
       </c>
       <c r="R15" t="n">
-        <v>7012870</v>
+        <v>7012941</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2682,7 +2673,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Enstaka garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Enstaka bålar av garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2702,7 +2693,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner</t>
+          <t>Barrdominerad skog med gran, tall, björk och gråal på frisk-fuktig och frisk mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2740,7 +2731,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120386770</v>
+        <v>120385563</v>
       </c>
       <c r="B16" t="n">
         <v>78542</v>
@@ -2783,10 +2774,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505101</v>
+        <v>505189</v>
       </c>
       <c r="R16" t="n">
-        <v>7012941</v>
+        <v>7012870</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2823,7 +2814,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Enstaka bålar av garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Enstaka garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2843,7 +2834,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och gråal på frisk-fuktig och frisk mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2881,7 +2872,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120386369</v>
+        <v>120385430</v>
       </c>
       <c r="B17" t="n">
         <v>78542</v>
@@ -2924,10 +2915,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505150</v>
+        <v>505292</v>
       </c>
       <c r="R17" t="n">
-        <v>7012938</v>
+        <v>7012763</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2964,7 +2955,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Enstaka bålar av garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Måttligt med garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2984,7 +2975,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och gråal på frisk-fuktig och frisk mark. Mestadels träd med klenare dimensioner</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2997,6 +2988,11 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Flera granar.</t>
+        </is>
+      </c>
       <c r="AM17" t="inlineStr">
         <is>
           <t>Gren på levande träd</t>
@@ -3004,7 +3000,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -3022,10 +3018,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120385195</v>
+        <v>120385814</v>
       </c>
       <c r="B18" t="n">
-        <v>79659</v>
+        <v>79623</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -3034,32 +3030,32 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -3069,13 +3065,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505272</v>
+        <v>505172</v>
       </c>
       <c r="R18" t="n">
-        <v>7012674</v>
+        <v>7012900</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3109,7 +3105,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Luddlav på en sälg där det även växer lunglav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Riklig påväxt av lunglav på en lutande gammal sälg. God föryngring med många färska yngre bålar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3129,7 +3125,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-, frisk-fuktig- och fuktig/blöt mark. Mestadels träd med klenare dimensioner</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -3144,7 +3140,7 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>En tvåstammig mindre grov sälg.</t>
+          <t>En gammal, lutande och nedböjd rätt grov flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -3154,7 +3150,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En tvåstammig mindre grov sälg.</t>
+          <t>Bark on living woody plant # Salix caprea # En gammal, lutande och nedböjd rätt grov flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3172,10 +3168,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120385430</v>
+        <v>120385195</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>79659</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3184,30 +3180,34 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3215,13 +3215,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505292</v>
+        <v>505272</v>
       </c>
       <c r="R19" t="n">
-        <v>7012763</v>
+        <v>7012674</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Måttligt med garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Luddlav på en sälg där det även växer lunglav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3275,32 +3275,32 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>Flera granar.</t>
+          <t>En tvåstammig mindre grov sälg.</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Bark on living woody plant # Salix caprea # En tvåstammig mindre grov sälg.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3318,7 +3318,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120384169</v>
+        <v>120383377</v>
       </c>
       <c r="B20" t="n">
         <v>79623</v>
@@ -3355,7 +3355,7 @@
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>505249</v>
+        <v>505309</v>
       </c>
       <c r="R20" t="n">
-        <v>7012657</v>
+        <v>7012591</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Lunglav på en lutande död sälg. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Riklig och bitvis tät påväxt av lunglav på en gammal sälg. Vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>En något smalare stående lutande död sälg.</t>
+          <t>En gammal flerstammig sälg med 44 cm i brösthöjdsdiameter. Sälgen utgörs delvis av död ved med hackspettshål.</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En något smalare stående lutande död sälg.</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En gammal flerstammig sälg med 44 cm i brösthöjdsdiameter. Sälgen utgörs delvis av död ved med hackspettshål.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 39941-2024 artfynd.xlsx
+++ b/artfynd/A 39941-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120348975</v>
+        <v>120349281</v>
       </c>
       <c r="B2" t="n">
         <v>78542</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505501</v>
+        <v>505418</v>
       </c>
       <c r="R2" t="n">
-        <v>7012484</v>
+        <v>7012531</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -758,7 +758,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Lite garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,12 +773,12 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Våtmark med gran</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Gles grandominerad skog på fuktig/blöt mark. Mestadels klena träd.</t>
+          <t>Klenvuxen grandominerad skog på frisk-fuktig- och fuktig mark. Skogsbruksåtgärd genom röjning förekommer här.</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1116,7 +1116,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120349281</v>
+        <v>120348975</v>
       </c>
       <c r="B5" t="n">
         <v>78542</v>
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505418</v>
+        <v>505501</v>
       </c>
       <c r="R5" t="n">
-        <v>7012531</v>
+        <v>7012484</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Lite garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1214,12 +1214,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Våtmark med gran</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Klenvuxen grandominerad skog på frisk-fuktig- och fuktig mark. Skogsbruksåtgärd genom röjning förekommer här.</t>
+          <t>Gles grandominerad skog på fuktig/blöt mark. Mestadels klena träd.</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1257,7 +1257,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120371664</v>
+        <v>120370644</v>
       </c>
       <c r="B6" t="n">
         <v>78542</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505323</v>
+        <v>505357</v>
       </c>
       <c r="R6" t="n">
-        <v>7012622</v>
+        <v>7012618</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flertalet granar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1375,17 +1375,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Flertalet granar.</t>
+          <t>En lutand</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flertalet granar.</t>
+          <t>Dead branch  # Picea abies # En lutand</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1403,10 +1403,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120370644</v>
+        <v>120370399</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1419,26 +1419,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1486,7 +1490,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Riklig påväxt av lunglav på en lutande sälg. Vissa av bålarna är fertila med apothecier. God föryngring med många färska yngre bålar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1511,27 +1515,27 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>En lutand</t>
+          <t>En lutande sälg med 31 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies # En lutand</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En lutande sälg med 31 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1549,10 +1553,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120371167</v>
+        <v>120371664</v>
       </c>
       <c r="B8" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1565,30 +1569,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505350</v>
+        <v>505323</v>
       </c>
       <c r="R8" t="n">
-        <v>7012628</v>
+        <v>7012622</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav på en sälg där det även växer bårdlav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Gott om långväxt garnlav på flertalet granar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1661,27 +1661,27 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>En sälg med 38 cm i brösthöjdsdiameter.</t>
+          <t>Flertalet granar.</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Medelgrov bark. # Salix caprea # En sälg med 38 cm i brösthöjdsdiameter.</t>
+          <t>Branch on living tree # Picea abies # Flertalet granar.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1699,10 +1699,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120371294</v>
+        <v>120369014</v>
       </c>
       <c r="B9" t="n">
-        <v>79658</v>
+        <v>79623</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1711,32 +1711,32 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1746,10 +1746,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505350</v>
+        <v>505356</v>
       </c>
       <c r="R9" t="n">
-        <v>7012628</v>
+        <v>7012590</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Bårdlav på en sälg där det även växer lunglav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Riklig påväxt av lunglav längs stor del av stammarna på en grov gammal sälg. Vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk, frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Grandominerad skog med inslag av tall, björk och sälg på frisk och frisk-fuktig mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>En sälg med 38 cm i brösthöjdsdiameter.</t>
+          <t>En gammal levande sälg med 60 cm i brösthöjdsdiameter. Består delvis av död ved med spår av hackspettar och är angripen av vedsvamp. Delar sig i två huvudstammar över brösthöjd.</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Medelgrov bark. # Salix caprea # En sälg med 38 cm i brösthöjdsdiameter.</t>
+          <t>Bark on living woody plant # Grov och fårad bark. # Salix caprea # En gammal levande sälg med 60 cm i brösthöjdsdiameter. Består delvis av död ved med spår av hackspettar och är angripen av vedsvamp. Delar sig i två huvudstammar över brösthöjd.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1849,7 +1849,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120369014</v>
+        <v>120371167</v>
       </c>
       <c r="B10" t="n">
         <v>79623</v>
@@ -1886,7 +1886,7 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505356</v>
+        <v>505350</v>
       </c>
       <c r="R10" t="n">
-        <v>7012590</v>
+        <v>7012628</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Riklig påväxt av lunglav längs stor del av stammarna på en grov gammal sälg. Vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Enstaka bålar av lunglav på en sälg där det även växer bårdlav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Grandominerad skog med inslag av tall, björk och sälg på frisk och frisk-fuktig mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk, frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>En gammal levande sälg med 60 cm i brösthöjdsdiameter. Består delvis av död ved med spår av hackspettar och är angripen av vedsvamp. Delar sig i två huvudstammar över brösthöjd.</t>
+          <t>En sälg med 38 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov och fårad bark. # Salix caprea # En gammal levande sälg med 60 cm i brösthöjdsdiameter. Består delvis av död ved med spår av hackspettar och är angripen av vedsvamp. Delar sig i två huvudstammar över brösthöjd.</t>
+          <t>Bark on living woody plant # Medelgrov bark. # Salix caprea # En sälg med 38 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1999,10 +1999,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120370399</v>
+        <v>120371294</v>
       </c>
       <c r="B11" t="n">
-        <v>79623</v>
+        <v>79658</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2011,32 +2011,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505357</v>
+        <v>505350</v>
       </c>
       <c r="R11" t="n">
-        <v>7012618</v>
+        <v>7012628</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Riklig påväxt av lunglav på en lutande sälg. Vissa av bålarna är fertila med apothecier. God föryngring med många färska yngre bålar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Bårdlav på en sälg där det även växer lunglav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>En lutande sälg med 31 cm i brösthöjdsdiameter.</t>
+          <t>En sälg med 38 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En lutande sälg med 31 cm i brösthöjdsdiameter.</t>
+          <t>Bark on living woody plant # Medelgrov bark. # Salix caprea # En sälg med 38 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120384169</v>
+        <v>120386369</v>
       </c>
       <c r="B12" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2165,30 +2165,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2196,10 +2192,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505249</v>
+        <v>505150</v>
       </c>
       <c r="R12" t="n">
-        <v>7012657</v>
+        <v>7012938</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2236,7 +2232,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Lunglav på en lutande död sälg. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Enstaka bålar av garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2256,32 +2252,27 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Barrdominerad skog med gran, tall, björk och gråal på frisk-fuktig och frisk mark. Mestadels träd med klenare dimensioner</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>En något smalare stående lutande död sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En något smalare stående lutande död sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2299,7 +2290,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120384713</v>
+        <v>120385814</v>
       </c>
       <c r="B13" t="n">
         <v>79623</v>
@@ -2346,13 +2337,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505272</v>
+        <v>505172</v>
       </c>
       <c r="R13" t="n">
-        <v>7012674</v>
+        <v>7012900</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2386,7 +2377,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rätt gott om lunglav på en sälg där det även växer luddlav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Riklig påväxt av lunglav på en lutande gammal sälg. God föryngring med många färska yngre bålar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2406,7 +2397,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-, frisk-fuktig- och fuktig/blöt mark. Mestadels träd med klenare dimensioner</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2421,7 +2412,7 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>En tvåstammig mindre grov sälg.</t>
+          <t>En gammal, lutande och nedböjd rätt grov flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -2431,7 +2422,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En tvåstammig mindre grov sälg.</t>
+          <t>Bark on living woody plant # Salix caprea # En gammal, lutande och nedböjd rätt grov flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2449,7 +2440,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120386369</v>
+        <v>120386770</v>
       </c>
       <c r="B14" t="n">
         <v>78542</v>
@@ -2492,10 +2483,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505150</v>
+        <v>505101</v>
       </c>
       <c r="R14" t="n">
-        <v>7012938</v>
+        <v>7012941</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2552,7 +2543,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och gråal på frisk-fuktig och frisk mark. Mestadels träd med klenare dimensioner</t>
+          <t>Barrdominerad skog med gran, tall, björk och gråal på frisk-fuktig och frisk mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2590,10 +2581,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120386770</v>
+        <v>120385195</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>79659</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2602,30 +2593,34 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2633,13 +2628,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505101</v>
+        <v>505272</v>
       </c>
       <c r="R15" t="n">
-        <v>7012941</v>
+        <v>7012674</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2673,7 +2668,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Enstaka bålar av garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Luddlav på en sälg där det även växer lunglav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2693,27 +2688,32 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och gråal på frisk-fuktig och frisk mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>En tvåstammig mindre grov sälg.</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En tvåstammig mindre grov sälg.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2731,10 +2731,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120385563</v>
+        <v>120384169</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2747,26 +2747,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2774,10 +2778,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505189</v>
+        <v>505249</v>
       </c>
       <c r="R16" t="n">
-        <v>7012870</v>
+        <v>7012657</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2814,7 +2818,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Enstaka garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Lunglav på en lutande död sälg. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2834,27 +2838,32 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>En något smalare stående lutande död sälg.</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En något smalare stående lutande död sälg.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2872,10 +2881,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120385430</v>
+        <v>120384713</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2888,26 +2897,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2915,13 +2928,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505292</v>
+        <v>505272</v>
       </c>
       <c r="R17" t="n">
-        <v>7012763</v>
+        <v>7012674</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2955,7 +2968,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Måttligt med garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Rätt gott om lunglav på en sälg där det även växer luddlav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2975,32 +2988,32 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>Flera granar.</t>
+          <t>En tvåstammig mindre grov sälg.</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Bark on living woody plant # Salix caprea # En tvåstammig mindre grov sälg.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -3018,10 +3031,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120385814</v>
+        <v>120385430</v>
       </c>
       <c r="B18" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -3034,30 +3047,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -3065,10 +3074,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505172</v>
+        <v>505292</v>
       </c>
       <c r="R18" t="n">
-        <v>7012900</v>
+        <v>7012763</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -3105,7 +3114,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Riklig påväxt av lunglav på en lutande gammal sälg. God föryngring med många färska yngre bålar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Måttligt med garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3125,32 +3134,32 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-, frisk-fuktig- och fuktig/blöt mark. Mestadels träd med klenare dimensioner</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>En gammal, lutande och nedböjd rätt grov flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Flera granar.</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En gammal, lutande och nedböjd rätt grov flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3168,10 +3177,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120385195</v>
+        <v>120383377</v>
       </c>
       <c r="B19" t="n">
-        <v>79659</v>
+        <v>79623</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3180,25 +3189,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -3215,13 +3224,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505272</v>
+        <v>505309</v>
       </c>
       <c r="R19" t="n">
-        <v>7012674</v>
+        <v>7012591</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3255,7 +3264,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Luddlav på en sälg där det även växer lunglav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Riklig och bitvis tät påväxt av lunglav på en gammal sälg. Vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3275,7 +3284,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -3290,7 +3299,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>En tvåstammig mindre grov sälg.</t>
+          <t>En gammal flerstammig sälg med 44 cm i brösthöjdsdiameter. Sälgen utgörs delvis av död ved med hackspettshål.</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -3300,7 +3309,7 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En tvåstammig mindre grov sälg.</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En gammal flerstammig sälg med 44 cm i brösthöjdsdiameter. Sälgen utgörs delvis av död ved med hackspettshål.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3318,10 +3327,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120383377</v>
+        <v>120385563</v>
       </c>
       <c r="B20" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3334,30 +3343,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3365,10 +3370,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>505309</v>
+        <v>505189</v>
       </c>
       <c r="R20" t="n">
-        <v>7012591</v>
+        <v>7012870</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3405,7 +3410,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Riklig och bitvis tät påväxt av lunglav på en gammal sälg. Vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Enstaka garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3425,32 +3430,27 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>En gammal flerstammig sälg med 44 cm i brösthöjdsdiameter. Sälgen utgörs delvis av död ved med hackspettshål.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En gammal flerstammig sälg med 44 cm i brösthöjdsdiameter. Sälgen utgörs delvis av död ved med hackspettshål.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>

--- a/artfynd/A 39941-2024 artfynd.xlsx
+++ b/artfynd/A 39941-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120349281</v>
+        <v>120349113</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -718,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505418</v>
+        <v>505456</v>
       </c>
       <c r="R2" t="n">
-        <v>7012531</v>
+        <v>7012524</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -758,7 +762,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Flertalet bålar av skrovellav på en gammal skadad sälg där det även växer lunglav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,32 +777,37 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Våtmark med barrträd</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Klenvuxen grandominerad skog på frisk-fuktig- och fuktig mark. Skogsbruksåtgärd genom röjning förekommer här.</t>
+          <t>Gles barrdominerad skog på fuktig/blöt mark. Mestadels klena träd.</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>En levande men mycket skadad sälg.</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En levande men mycket skadad sälg.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -816,10 +825,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120349113</v>
+        <v>120349281</v>
       </c>
       <c r="B3" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -832,30 +841,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -863,10 +868,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505456</v>
+        <v>505418</v>
       </c>
       <c r="R3" t="n">
-        <v>7012524</v>
+        <v>7012531</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -903,7 +908,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Flertalet bålar av skrovellav på en gammal skadad sälg där det även växer lunglav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,37 +923,32 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Våtmark med barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Gles barrdominerad skog på fuktig/blöt mark. Mestadels klena träd.</t>
+          <t>Klenvuxen grandominerad skog på frisk-fuktig- och fuktig mark. Skogsbruksåtgärd genom röjning förekommer här.</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>En levande men mycket skadad sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En levande men mycket skadad sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1403,10 +1403,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120370399</v>
+        <v>120371664</v>
       </c>
       <c r="B7" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1419,30 +1419,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1450,10 +1446,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505357</v>
+        <v>505323</v>
       </c>
       <c r="R7" t="n">
-        <v>7012618</v>
+        <v>7012622</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1490,7 +1486,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Riklig påväxt av lunglav på en lutande sälg. Vissa av bålarna är fertila med apothecier. God föryngring med många färska yngre bålar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Gott om långväxt garnlav på flertalet granar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1515,27 +1511,27 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>En lutande sälg med 31 cm i brösthöjdsdiameter.</t>
+          <t>Flertalet granar.</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En lutande sälg med 31 cm i brösthöjdsdiameter.</t>
+          <t>Branch on living tree # Picea abies # Flertalet granar.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1553,10 +1549,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120371664</v>
+        <v>120371294</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>79658</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1565,20 +1561,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1588,7 +1584,11 @@
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505323</v>
+        <v>505350</v>
       </c>
       <c r="R8" t="n">
-        <v>7012622</v>
+        <v>7012628</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flertalet granar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Bårdlav på en sälg där det även växer lunglav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1661,27 +1661,27 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>Flertalet granar.</t>
+          <t>En sälg med 38 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flertalet granar.</t>
+          <t>Bark on living woody plant # Medelgrov bark. # Salix caprea # En sälg med 38 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1699,7 +1699,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120369014</v>
+        <v>120371167</v>
       </c>
       <c r="B9" t="n">
         <v>79623</v>
@@ -1736,7 +1736,7 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1746,10 +1746,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505356</v>
+        <v>505350</v>
       </c>
       <c r="R9" t="n">
-        <v>7012590</v>
+        <v>7012628</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Riklig påväxt av lunglav längs stor del av stammarna på en grov gammal sälg. Vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Enstaka bålar av lunglav på en sälg där det även växer bårdlav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Grandominerad skog med inslag av tall, björk och sälg på frisk och frisk-fuktig mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk, frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>En gammal levande sälg med 60 cm i brösthöjdsdiameter. Består delvis av död ved med spår av hackspettar och är angripen av vedsvamp. Delar sig i två huvudstammar över brösthöjd.</t>
+          <t>En sälg med 38 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov och fårad bark. # Salix caprea # En gammal levande sälg med 60 cm i brösthöjdsdiameter. Består delvis av död ved med spår av hackspettar och är angripen av vedsvamp. Delar sig i två huvudstammar över brösthöjd.</t>
+          <t>Bark on living woody plant # Medelgrov bark. # Salix caprea # En sälg med 38 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1849,7 +1849,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120371167</v>
+        <v>120370399</v>
       </c>
       <c r="B10" t="n">
         <v>79623</v>
@@ -1886,7 +1886,7 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1896,10 +1896,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505350</v>
+        <v>505357</v>
       </c>
       <c r="R10" t="n">
-        <v>7012628</v>
+        <v>7012618</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav på en sälg där det även växer bårdlav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Riklig påväxt av lunglav på en lutande sälg. Vissa av bålarna är fertila med apothecier. God föryngring med många färska yngre bålar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>En sälg med 38 cm i brösthöjdsdiameter.</t>
+          <t>En lutande sälg med 31 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Medelgrov bark. # Salix caprea # En sälg med 38 cm i brösthöjdsdiameter.</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En lutande sälg med 31 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1999,10 +1999,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120371294</v>
+        <v>120369014</v>
       </c>
       <c r="B11" t="n">
-        <v>79658</v>
+        <v>79623</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2011,32 +2011,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505350</v>
+        <v>505356</v>
       </c>
       <c r="R11" t="n">
-        <v>7012628</v>
+        <v>7012590</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Bårdlav på en sälg där det även växer lunglav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Riklig påväxt av lunglav längs stor del av stammarna på en grov gammal sälg. Vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk, frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Grandominerad skog med inslag av tall, björk och sälg på frisk och frisk-fuktig mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>En sälg med 38 cm i brösthöjdsdiameter.</t>
+          <t>En gammal levande sälg med 60 cm i brösthöjdsdiameter. Består delvis av död ved med spår av hackspettar och är angripen av vedsvamp. Delar sig i två huvudstammar över brösthöjd.</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Medelgrov bark. # Salix caprea # En sälg med 38 cm i brösthöjdsdiameter.</t>
+          <t>Bark on living woody plant # Grov och fårad bark. # Salix caprea # En gammal levande sälg med 60 cm i brösthöjdsdiameter. Består delvis av död ved med spår av hackspettar och är angripen av vedsvamp. Delar sig i två huvudstammar över brösthöjd.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2149,10 +2149,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120386369</v>
+        <v>120384169</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2165,26 +2165,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2192,10 +2196,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505150</v>
+        <v>505249</v>
       </c>
       <c r="R12" t="n">
-        <v>7012938</v>
+        <v>7012657</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2232,7 +2236,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Enstaka bålar av garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Lunglav på en lutande död sälg. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2252,27 +2256,32 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och gråal på frisk-fuktig och frisk mark. Mestadels träd med klenare dimensioner</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>En något smalare stående lutande död sälg.</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea # En något smalare stående lutande död sälg.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2290,7 +2299,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120385814</v>
+        <v>120384713</v>
       </c>
       <c r="B13" t="n">
         <v>79623</v>
@@ -2337,13 +2346,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505172</v>
+        <v>505272</v>
       </c>
       <c r="R13" t="n">
-        <v>7012900</v>
+        <v>7012674</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2377,7 +2386,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Riklig påväxt av lunglav på en lutande gammal sälg. God föryngring med många färska yngre bålar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Rätt gott om lunglav på en sälg där det även växer luddlav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2397,7 +2406,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-, frisk-fuktig- och fuktig/blöt mark. Mestadels träd med klenare dimensioner</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2412,7 +2421,7 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>En gammal, lutande och nedböjd rätt grov flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>En tvåstammig mindre grov sälg.</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -2422,7 +2431,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En gammal, lutande och nedböjd rätt grov flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Bark on living woody plant # Salix caprea # En tvåstammig mindre grov sälg.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2581,10 +2590,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120385195</v>
+        <v>120385814</v>
       </c>
       <c r="B15" t="n">
-        <v>79659</v>
+        <v>79623</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2593,32 +2602,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2628,13 +2637,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505272</v>
+        <v>505172</v>
       </c>
       <c r="R15" t="n">
-        <v>7012674</v>
+        <v>7012900</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2668,7 +2677,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Luddlav på en sälg där det även växer lunglav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Riklig påväxt av lunglav på en lutande gammal sälg. God föryngring med många färska yngre bålar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2688,7 +2697,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-, frisk-fuktig- och fuktig/blöt mark. Mestadels träd med klenare dimensioner</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2703,7 +2712,7 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>En tvåstammig mindre grov sälg.</t>
+          <t>En gammal, lutande och nedböjd rätt grov flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -2713,7 +2722,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En tvåstammig mindre grov sälg.</t>
+          <t>Bark on living woody plant # Salix caprea # En gammal, lutande och nedböjd rätt grov flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2731,7 +2740,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120384169</v>
+        <v>120383377</v>
       </c>
       <c r="B16" t="n">
         <v>79623</v>
@@ -2768,7 +2777,7 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2778,10 +2787,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505249</v>
+        <v>505309</v>
       </c>
       <c r="R16" t="n">
-        <v>7012657</v>
+        <v>7012591</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2818,7 +2827,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Lunglav på en lutande död sälg. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Riklig och bitvis tät påväxt av lunglav på en gammal sälg. Vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2853,17 +2862,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>En något smalare stående lutande död sälg.</t>
+          <t>En gammal flerstammig sälg med 44 cm i brösthöjdsdiameter. Sälgen utgörs delvis av död ved med hackspettshål.</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En något smalare stående lutande död sälg.</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En gammal flerstammig sälg med 44 cm i brösthöjdsdiameter. Sälgen utgörs delvis av död ved med hackspettshål.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2881,10 +2890,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120384713</v>
+        <v>120385563</v>
       </c>
       <c r="B17" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2897,30 +2906,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2928,13 +2933,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505272</v>
+        <v>505189</v>
       </c>
       <c r="R17" t="n">
-        <v>7012674</v>
+        <v>7012870</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2968,7 +2973,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rätt gott om lunglav på en sälg där det även växer luddlav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Enstaka garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2988,32 +2993,27 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>En tvåstammig mindre grov sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En tvåstammig mindre grov sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -3031,10 +3031,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120385430</v>
+        <v>120385195</v>
       </c>
       <c r="B18" t="n">
-        <v>78542</v>
+        <v>79659</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -3043,30 +3043,34 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -3074,13 +3078,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505292</v>
+        <v>505272</v>
       </c>
       <c r="R18" t="n">
-        <v>7012763</v>
+        <v>7012674</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3114,7 +3118,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Måttligt med garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Luddlav på en sälg där det även växer lunglav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3134,32 +3138,32 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>Flera granar.</t>
+          <t>En tvåstammig mindre grov sälg.</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Bark on living woody plant # Salix caprea # En tvåstammig mindre grov sälg.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3177,10 +3181,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120383377</v>
+        <v>120385430</v>
       </c>
       <c r="B19" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -3193,30 +3197,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505309</v>
+        <v>505292</v>
       </c>
       <c r="R19" t="n">
-        <v>7012591</v>
+        <v>7012763</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Riklig och bitvis tät påväxt av lunglav på en gammal sälg. Vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Måttligt med garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3289,27 +3289,27 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>En gammal flerstammig sälg med 44 cm i brösthöjdsdiameter. Sälgen utgörs delvis av död ved med hackspettshål.</t>
+          <t>Flera granar.</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En gammal flerstammig sälg med 44 cm i brösthöjdsdiameter. Sälgen utgörs delvis av död ved med hackspettshål.</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3327,7 +3327,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120385563</v>
+        <v>120386369</v>
       </c>
       <c r="B20" t="n">
         <v>78542</v>
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>505189</v>
+        <v>505150</v>
       </c>
       <c r="R20" t="n">
-        <v>7012870</v>
+        <v>7012938</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Enstaka garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Enstaka bålar av garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner</t>
+          <t>Barrdominerad skog med gran, tall, björk och gråal på frisk-fuktig och frisk mark. Mestadels träd med klenare dimensioner</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">

--- a/artfynd/A 39941-2024 artfynd.xlsx
+++ b/artfynd/A 39941-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>120349113</v>
       </c>
       <c r="B2" t="n">
-        <v>79646</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -825,19 +820,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120348975</v>
+        <v>120348771</v>
       </c>
       <c r="B3" t="n">
-        <v>78564</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -868,13 +858,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>505501</v>
+        <v>505525</v>
       </c>
       <c r="R3" t="n">
-        <v>7012484</v>
+        <v>7012426</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -908,7 +898,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Lite garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Relativt gott om garnlav på gran. Obs! Fyndplatsen ligger på gränsen till en avverkningsanmälan med beteckning A 39941-2024</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,7 +918,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Gles grandominerad skog på fuktig/blöt mark. Mestadels klena träd.</t>
+          <t>Gles grandominerad skog på fuktig/blöt- och frisk-fuktig mark. Mestadels klena träd.</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -948,7 +938,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Torra döda grenar på en levande gran. # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -966,19 +956,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120349281</v>
+        <v>120348975</v>
       </c>
       <c r="B4" t="n">
-        <v>78564</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1009,10 +994,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>505418</v>
+        <v>505501</v>
       </c>
       <c r="R4" t="n">
-        <v>7012531</v>
+        <v>7012484</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1049,7 +1034,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Lite garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1064,12 +1049,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Våtmark med gran</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Klenvuxen grandominerad skog på frisk-fuktig- och fuktig mark. Skogsbruksåtgärd genom röjning förekommer här.</t>
+          <t>Gles grandominerad skog på fuktig/blöt mark. Mestadels klena träd.</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1107,46 +1092,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120349153</v>
+        <v>120349281</v>
       </c>
       <c r="B5" t="n">
-        <v>79645</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1154,10 +1130,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>505456</v>
+        <v>505418</v>
       </c>
       <c r="R5" t="n">
-        <v>7012524</v>
+        <v>7012531</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1194,7 +1170,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Flertalet bålar av lunglav på en gammal skadad sälg där det även växer skrovellav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1209,37 +1185,32 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Våtmark med barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Gles barrdominerad skog på fuktig/blöt mark. Mestadels klena träd.</t>
+          <t>Klenvuxen grandominerad skog på frisk-fuktig- och fuktig mark. Skogsbruksåtgärd genom röjning förekommer här.</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>En levande men mycket skadad sälg.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En levande men mycket skadad sälg.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1257,19 +1228,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120371664</v>
+        <v>120370644</v>
       </c>
       <c r="B6" t="n">
-        <v>78564</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1300,10 +1266,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505323</v>
+        <v>505357</v>
       </c>
       <c r="R6" t="n">
-        <v>7012622</v>
+        <v>7012618</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1340,7 +1306,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på flertalet granar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Långväxt garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1375,17 +1341,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Flertalet granar.</t>
+          <t>En lutand</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Död gren</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flertalet granar.</t>
+          <t>Dead branch  # Picea abies # En lutand</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1403,46 +1369,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120371167</v>
+        <v>120371664</v>
       </c>
       <c r="B7" t="n">
-        <v>79645</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1450,10 +1407,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505350</v>
+        <v>505323</v>
       </c>
       <c r="R7" t="n">
-        <v>7012628</v>
+        <v>7012622</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1490,7 +1447,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Enstaka bålar av lunglav på en sälg där det även växer bårdlav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Gott om långväxt garnlav på flertalet granar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1515,27 +1472,27 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>En sälg med 38 cm i brösthöjdsdiameter.</t>
+          <t>Flertalet granar.</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Medelgrov bark. # Salix caprea # En sälg med 38 cm i brösthöjdsdiameter.</t>
+          <t>Branch on living tree # Picea abies # Flertalet granar.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1553,19 +1510,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120370644</v>
+        <v>120385430</v>
       </c>
       <c r="B8" t="n">
-        <v>78564</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1596,10 +1548,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505357</v>
+        <v>505292</v>
       </c>
       <c r="R8" t="n">
-        <v>7012618</v>
+        <v>7012763</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1636,7 +1588,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Långväxt garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Måttligt med garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1656,7 +1608,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk, frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1671,17 +1623,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>En lutand</t>
+          <t>Flera granar.</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Död gren</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Dead branch  # Picea abies # En lutand</t>
+          <t>Branch on living tree # Picea abies # Flera granar.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1699,32 +1651,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120371294</v>
+        <v>120385563</v>
       </c>
       <c r="B9" t="n">
-        <v>79680</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1734,11 +1681,7 @@
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1746,10 +1689,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505350</v>
+        <v>505189</v>
       </c>
       <c r="R9" t="n">
-        <v>7012628</v>
+        <v>7012870</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1786,7 +1729,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Bårdlav på en sälg där det även växer lunglav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Enstaka garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1806,32 +1749,27 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk, frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>En sälg med 38 cm i brösthöjdsdiameter.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Medelgrov bark. # Salix caprea # En sälg med 38 cm i brösthöjdsdiameter.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1849,46 +1787,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120370399</v>
+        <v>120386369</v>
       </c>
       <c r="B10" t="n">
-        <v>79645</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1896,10 +1825,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>505357</v>
+        <v>505150</v>
       </c>
       <c r="R10" t="n">
-        <v>7012618</v>
+        <v>7012938</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1936,7 +1865,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Riklig påväxt av lunglav på en lutande sälg. Vissa av bålarna är fertila med apothecier. God föryngring med många färska yngre bålar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Enstaka bålar av garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1956,32 +1885,27 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk, frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Barrdominerad skog med gran, tall, björk och gråal på frisk-fuktig och frisk mark. Mestadels träd med klenare dimensioner</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>En lutande sälg med 31 cm i brösthöjdsdiameter.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En lutande sälg med 31 cm i brösthöjdsdiameter.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1999,46 +1923,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120369014</v>
+        <v>120386770</v>
       </c>
       <c r="B11" t="n">
-        <v>79645</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -2046,10 +1961,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>505356</v>
+        <v>505101</v>
       </c>
       <c r="R11" t="n">
-        <v>7012590</v>
+        <v>7012941</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2086,7 +2001,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Riklig påväxt av lunglav längs stor del av stammarna på en grov gammal sälg. Vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Enstaka bålar av garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2101,37 +2016,32 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>Grandominerad skog med inslag av tall, björk och sälg på frisk och frisk-fuktig mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Barrdominerad skog med gran, tall, björk och gråal på frisk-fuktig och frisk mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>En gammal levande sälg med 60 cm i brösthöjdsdiameter. Består delvis av död ved med spår av hackspettar och är angripen av vedsvamp. Delar sig i två huvudstammar över brösthöjd.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov och fårad bark. # Salix caprea # En gammal levande sälg med 60 cm i brösthöjdsdiameter. Består delvis av död ved med spår av hackspettar och är angripen av vedsvamp. Delar sig i två huvudstammar över brösthöjd.</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2149,15 +2059,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120384169</v>
+        <v>120349153</v>
       </c>
       <c r="B12" t="n">
-        <v>79645</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2196,10 +2101,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>505249</v>
+        <v>505456</v>
       </c>
       <c r="R12" t="n">
-        <v>7012657</v>
+        <v>7012524</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2236,7 +2141,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Lunglav på en lutande död sälg. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Flertalet bålar av lunglav på en gammal skadad sälg där det även växer skrovellav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2251,12 +2156,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Våtmark med barrträd</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Gles barrdominerad skog på fuktig/blöt mark. Mestadels klena träd.</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2271,17 +2176,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>En något smalare stående lutande död sälg.</t>
+          <t>En levande men mycket skadad sälg.</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea # En något smalare stående lutande död sälg.</t>
+          <t>Bark on living woody plant # Salix caprea # En levande men mycket skadad sälg.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2299,15 +2204,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120385814</v>
+        <v>120369014</v>
       </c>
       <c r="B13" t="n">
-        <v>79645</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2336,7 +2236,7 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2346,10 +2246,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>505172</v>
+        <v>505356</v>
       </c>
       <c r="R13" t="n">
-        <v>7012900</v>
+        <v>7012590</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2386,7 +2286,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Riklig påväxt av lunglav på en lutande gammal sälg. God föryngring med många färska yngre bålar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Riklig påväxt av lunglav längs stor del av stammarna på en grov gammal sälg. Vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2401,12 +2301,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-, frisk-fuktig- och fuktig/blöt mark. Mestadels träd med klenare dimensioner</t>
+          <t>Grandominerad skog med inslag av tall, björk och sälg på frisk och frisk-fuktig mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -2421,7 +2321,7 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>En gammal, lutande och nedböjd rätt grov flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>En gammal levande sälg med 60 cm i brösthöjdsdiameter. Består delvis av död ved med spår av hackspettar och är angripen av vedsvamp. Delar sig i två huvudstammar över brösthöjd.</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -2431,7 +2331,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En gammal, lutande och nedböjd rätt grov flerstammig sälg som delvis utgörs av död ved.</t>
+          <t>Bark on living woody plant # Grov och fårad bark. # Salix caprea # En gammal levande sälg med 60 cm i brösthöjdsdiameter. Består delvis av död ved med spår av hackspettar och är angripen av vedsvamp. Delar sig i två huvudstammar över brösthöjd.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2449,37 +2349,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120385195</v>
+        <v>120370399</v>
       </c>
       <c r="B14" t="n">
-        <v>79681</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2496,13 +2391,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>505272</v>
+        <v>505357</v>
       </c>
       <c r="R14" t="n">
-        <v>7012674</v>
+        <v>7012618</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2536,7 +2431,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Luddlav på en sälg där det även växer lunglav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Riklig påväxt av lunglav på en lutande sälg. Vissa av bålarna är fertila med apothecier. God föryngring med många färska yngre bålar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2556,7 +2451,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk, frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2571,7 +2466,7 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>En tvåstammig mindre grov sälg.</t>
+          <t>En lutande sälg med 31 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -2581,7 +2476,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En tvåstammig mindre grov sälg.</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En lutande sälg med 31 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2599,15 +2494,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120386770</v>
+        <v>120371167</v>
       </c>
       <c r="B15" t="n">
-        <v>78564</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2615,26 +2505,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2642,10 +2536,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>505101</v>
+        <v>505350</v>
       </c>
       <c r="R15" t="n">
-        <v>7012941</v>
+        <v>7012628</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2682,7 +2576,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Enstaka bålar av garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Enstaka bålar av lunglav på en sälg där det även växer bårdlav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2702,27 +2596,32 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och gråal på frisk-fuktig och frisk mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk, frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>En sälg med 38 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Medelgrov bark. # Salix caprea # En sälg med 38 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2740,15 +2639,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120385430</v>
+        <v>120383377</v>
       </c>
       <c r="B16" t="n">
-        <v>78564</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2756,26 +2650,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2783,10 +2681,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>505292</v>
+        <v>505309</v>
       </c>
       <c r="R16" t="n">
-        <v>7012763</v>
+        <v>7012591</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2823,7 +2721,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Måttligt med garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Riklig och bitvis tät påväxt av lunglav på en gammal sälg. Vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2848,27 +2746,27 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>Flera granar.</t>
+          <t>En gammal flerstammig sälg med 44 cm i brösthöjdsdiameter. Sälgen utgörs delvis av död ved med hackspettshål.</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies # Flera granar.</t>
+          <t>Bark on living woody plant # Grov bark. # Salix caprea # En gammal flerstammig sälg med 44 cm i brösthöjdsdiameter. Sälgen utgörs delvis av död ved med hackspettshål.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2886,15 +2784,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120383377</v>
+        <v>120384169</v>
       </c>
       <c r="B17" t="n">
-        <v>79645</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2923,7 +2816,7 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2933,10 +2826,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>505309</v>
+        <v>505249</v>
       </c>
       <c r="R17" t="n">
-        <v>7012591</v>
+        <v>7012657</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2973,7 +2866,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Riklig och bitvis tät påväxt av lunglav på en gammal sälg. Vissa av bålarna är fertila med apothecier. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Lunglav på en lutande död sälg. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3008,17 +2901,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>En gammal flerstammig sälg med 44 cm i brösthöjdsdiameter. Sälgen utgörs delvis av död ved med hackspettshål.</t>
+          <t>En något smalare stående lutande död sälg.</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Grov bark. # Salix caprea # En gammal flerstammig sälg med 44 cm i brösthöjdsdiameter. Sälgen utgörs delvis av död ved med hackspettshål.</t>
+          <t>Bark of dead wood # Salix caprea # En något smalare stående lutande död sälg.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -3036,15 +2929,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120385563</v>
+        <v>120384713</v>
       </c>
       <c r="B18" t="n">
-        <v>78564</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3052,26 +2940,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -3079,13 +2971,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>505189</v>
+        <v>505272</v>
       </c>
       <c r="R18" t="n">
-        <v>7012870</v>
+        <v>7012674</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3119,7 +3011,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Enstaka garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Rätt gott om lunglav på en sälg där det även växer luddlav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3139,27 +3031,32 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig/blöt mark. Mestadels träd med klenare dimensioner</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>En tvåstammig mindre grov sälg.</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En tvåstammig mindre grov sälg.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -3177,15 +3074,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120386369</v>
+        <v>120385814</v>
       </c>
       <c r="B19" t="n">
-        <v>78564</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3193,26 +3085,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -3220,10 +3116,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>505150</v>
+        <v>505172</v>
       </c>
       <c r="R19" t="n">
-        <v>7012938</v>
+        <v>7012900</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -3260,7 +3156,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Enstaka bålar av garnlav på gran. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Riklig påväxt av lunglav på en lutande gammal sälg. God föryngring med många färska yngre bålar. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3280,27 +3176,32 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och gråal på frisk-fuktig och frisk mark. Mestadels träd med klenare dimensioner</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-, frisk-fuktig- och fuktig/blöt mark. Mestadels träd med klenare dimensioner</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>En gammal, lutande och nedböjd rätt grov flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea # En gammal, lutande och nedböjd rätt grov flerstammig sälg som delvis utgörs av död ved.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3318,37 +3219,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120384713</v>
+        <v>120371294</v>
       </c>
       <c r="B20" t="n">
-        <v>79645</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3365,13 +3261,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>505272</v>
+        <v>505350</v>
       </c>
       <c r="R20" t="n">
-        <v>7012674</v>
+        <v>7012628</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3405,7 +3301,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Rätt gott om lunglav på en sälg där det även växer luddlav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+          <t>Bårdlav på en sälg där det även växer lunglav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3425,7 +3321,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk, frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3440,7 +3336,7 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>En tvåstammig mindre grov sälg.</t>
+          <t>En sälg med 38 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -3450,7 +3346,7 @@
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea # En tvåstammig mindre grov sälg.</t>
+          <t>Bark on living woody plant # Medelgrov bark. # Salix caprea # En sälg med 38 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3465,6 +3361,284 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120385195</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80468</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Björnmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>505272</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7012674</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Luddlav på en sälg där det även växer lunglav. Obs! Fyndplatsen ligger inom en avverkningsanmälan med beteckning A 39941-2024.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Barrdominerad skog med gran, tall, björk och sälg på frisk-fuktig och fuktig mark. Mestadels träd med klenare dimensioner.</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>En tvåstammig mindre grov sälg.</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea # En tvåstammig mindre grov sälg.</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120348657</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>frukt-/fröspridning</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Björnmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>505525</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7012426</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Observation av 1 st fröställning av fläcknycklar. Obs! Fyndplatsen ligger på gränsen till en avverkningsanmälan med beteckning A 39941-2024.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Våtmark med gran</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Gles grandominerad skog på fuktig/blöt- och frisk-fuktig mark. Mestadels klena träd.</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39941-2024 artfynd.xlsx
+++ b/artfynd/A 39941-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -817,6 +822,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120349113</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -953,6 +963,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348771</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1089,6 +1104,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348975</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1225,6 +1245,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120349281</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1366,6 +1391,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120370644</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1507,6 +1537,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120371664</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1648,6 +1683,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120385430</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1784,6 +1824,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120385563</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1920,6 +1965,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120386369</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2056,6 +2106,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120386770</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2201,6 +2256,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120349153</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2346,6 +2406,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120369014</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2491,6 +2556,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120370399</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2636,6 +2706,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120371167</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2781,6 +2856,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120383377</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2926,6 +3006,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120384169</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3071,6 +3156,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120384713</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3216,6 +3306,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120385814</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3361,6 +3456,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120371294</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3506,6 +3606,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120385195</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3639,8 +3744,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348657</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>